--- a/Vo_Dinh_Tan.xlsx
+++ b/Vo_Dinh_Tan.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12710" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="12110" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week1" sheetId="2" r:id="rId2"/>
     <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
   <si>
     <t>STT</t>
   </si>
@@ -205,6 +205,48 @@
   </si>
   <si>
     <t>Phản hồi: AI cung cấp 3 tài liệu từ ACM và IEEE. Kiểm chứng: Tôi kiểm tra Google Scholar và xác nhận 2/3 bài liên quan trực tiếp đến use-case driven development. Một bài quá cũ nên tôi không sử dụng trong báo cáo cuối cùng.</t>
+  </si>
+  <si>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>“Trong UML nên dùng Composition hay Aggregation giữa Booking và Payment?”</t>
+  </si>
+  <si>
+    <t>AI đề xuất dùng Composition vì Payment phụ thuộc vào vòng đời của Booking. Sau khi phân tích yêu cầu bài toán, tôi quyết định dùng Composition vì nếu Booking bị hủy thì Payment cũng không còn ý nghĩa tồn tại độc lập.</t>
+  </si>
+  <si>
+    <t>Decomposition</t>
+  </si>
+  <si>
+    <t>“Đối với hệ thống thuê xe nhỏ nên dùng Layered Architecture hay Microservices?”</t>
+  </si>
+  <si>
+    <t>AI gợi ý dùng Layered Architecture do hệ thống không quá lớn và dễ mô hình hóa UML hơn. Tôi chọn Layered Architecture vì phù hợp phạm vi đề thi và giúp các sơ đồ thống nhất hơn.</t>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>“Làm thế nào để thể hiện Repository Pattern trong Class Diagram UML?”</t>
+  </si>
+  <si>
+    <t>AI đề xuất tạo interface IGenericRepository&lt;T&gt; và để các Repository implement interface này. Tôi áp dụng cách này để tách biệt business logic và data access theo đúng yêu cầu đề bài.</t>
+  </si>
+  <si>
+    <t>“Multiplicity giữa Customer và Booking nên là gì?”</t>
+  </si>
+  <si>
+    <t>AI đề xuất quan hệ một-nhiều vì một Customer có thể tạo nhiều Booking. Tôi kiểm tra lại business requirement và quyết định sử dụng multiplicity 1..*.</t>
+  </si>
+  <si>
+    <t>Algorithms / Workflow</t>
+  </si>
+  <si>
+    <t>“Nên đặt xử lý thanh toán trong Entity hay Service class?”</t>
+  </si>
+  <si>
+    <t>AI đề xuất tạo PaymentService để xử lý business logic liên quan đến thanh toán. Tôi đồng ý vì cách này giúp Entity không chứa quá nhiều trách nhiệm và phù hợp mô hình Layered Architecture.</t>
   </si>
 </sst>
 </file>
@@ -848,13 +890,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1238,58 +1283,58 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" ht="70" spans="1:5">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="56" spans="1:5">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" ht="70" spans="1:5">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" ht="84" spans="1:5">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1327,282 +1372,282 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" ht="70" spans="1:5">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" ht="84" spans="1:5">
-      <c r="A3" s="3">
+    <row r="3" ht="70" spans="1:5">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="84" spans="1:5">
-      <c r="A4" s="3">
+    <row r="4" ht="70" spans="1:5">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="70" spans="1:5">
-      <c r="A5" s="3">
+    <row r="5" ht="56" spans="1:5">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" ht="56" spans="1:5">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" ht="56" spans="1:5">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" ht="70" spans="1:5">
-      <c r="A8" s="3">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" ht="56" spans="1:5">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" ht="56" spans="1:5">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="56" spans="1:5">
-      <c r="A11" s="3">
+    <row r="11" ht="42" spans="1:5">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" ht="70" spans="1:5">
-      <c r="A12" s="3">
+    <row r="12" ht="56" spans="1:5">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" ht="70" spans="1:5">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="14" ht="56" spans="1:5">
-      <c r="A14" s="3">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="70" spans="1:5">
-      <c r="A15" s="3">
+    <row r="15" ht="56" spans="1:5">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" ht="70" spans="1:5">
-      <c r="A16" s="3">
+    <row r="16" ht="56" spans="1:5">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" ht="70" spans="1:4">
-      <c r="A17" s="3">
+    <row r="17" ht="56" spans="1:4">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" ht="70" spans="1:4">
-      <c r="A18" s="3">
+    <row r="18" ht="56" spans="1:4">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" ht="56" spans="1:4">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" ht="70" spans="1:4">
-      <c r="A20" s="3">
+    <row r="20" ht="56" spans="1:4">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" ht="70" spans="1:4">
-      <c r="A21" s="3">
+    <row r="21" ht="56" spans="1:4">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1626,9 +1671,191 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8666666666667" customWidth="1"/>
+    <col min="3" max="3" width="30.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="50.5833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="49" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="56" spans="1:5">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" ht="42" spans="1:5">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" ht="56" spans="1:5">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" ht="42" spans="1:5">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" ht="56" spans="1:5">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Vo_Dinh_Tan.xlsx
+++ b/Vo_Dinh_Tan.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12110" activeTab="3"/>
+    <workbookView windowWidth="24750" windowHeight="12710" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week1" sheetId="2" r:id="rId2"/>
     <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
     <sheet name="Week3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week4" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="80">
   <si>
     <t>STT</t>
   </si>
@@ -234,9 +235,6 @@
     <t>AI đề xuất tạo interface IGenericRepository&lt;T&gt; và để các Repository implement interface này. Tôi áp dụng cách này để tách biệt business logic và data access theo đúng yêu cầu đề bài.</t>
   </si>
   <si>
-    <t>“Multiplicity giữa Customer và Booking nên là gì?”</t>
-  </si>
-  <si>
     <t>AI đề xuất quan hệ một-nhiều vì một Customer có thể tạo nhiều Booking. Tôi kiểm tra lại business requirement và quyết định sử dụng multiplicity 1..*.</t>
   </si>
   <si>
@@ -247,6 +245,36 @@
   </si>
   <si>
     <t>AI đề xuất tạo PaymentService để xử lý business logic liên quan đến thanh toán. Tôi đồng ý vì cách này giúp Entity không chứa quá nhiều trách nhiệm và phù hợp mô hình Layered Architecture.</t>
+  </si>
+  <si>
+    <t>"Đối với Use Case 'Create Booking and Pay Deposit', những thành phần nào cần xuất hiện trong Sequence Diagram theo kiến trúc Layered Architecture?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Customer, BookingUI, BookingController, BookingService, CarRepository, BookingRepository, PaymentService, Booking Entity và Car Entity. Quyết định: Tôi đối chiếu yêu cầu đề bài và xác nhận các thành phần UI, service/controller, repository và domain entities đều được đề cập. Tôi sử dụng cấu trúc này làm nền tảng cho Sequence Diagram.</t>
+  </si>
+  <si>
+    <t>"Hãy mô tả tuần tự các bước xử lý của Use Case Create Booking and Pay Deposit."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả luồng gồm chọn xe → kiểm tra xe trống → tạo booking → thanh toán đặt cọc → xác nhận hoặc hủy booking. Kiểm chứng: Tôi so sánh với mô tả đề bài và thấy phù hợp. Tôi giữ nguyên flow chính và bổ sung tên các lời gọi phương thức cụ thể giữa các thành phần.</t>
+  </si>
+  <si>
+    <t>"Repository Pattern nên được thể hiện như thế nào trong Sequence Diagram của chức năng đặt xe?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho rằng Service sẽ gọi trực tiếp database để kiểm tra xe và lưu booking. Kiểm chứng: Đây là AI hallucination vì đề bài yêu cầu Repository Pattern phải được thể hiện rõ. Tôi sửa lại bằng cách để BookingService gọi CarRepository.checkAvailability() và BookingRepository.saveBooking() thay vì truy cập database trực tiếp.</t>
+  </si>
+  <si>
+    <t>"Trong Use Case này cần sử dụng alt fragment ở những vị trí nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác định hai nhánh điều kiện gồm Car Available/Not Available và Payment Success/Payment Failed. Kiểm chứng: Tôi đối chiếu với yêu cầu đề và xác nhận hoàn toàn chính xác. Tôi sử dụng hai alt fragment này trong Sequence Diagram cuối cùng.</t>
+  </si>
+  <si>
+    <t>"Theo UML Sequence Diagram, khi thanh toán thất bại thì nên xử lý booking như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất cập nhật trạng thái booking thành Cancelled thông qua BookingRepository. Kiểm chứng: Tôi tham khảo UML modeling guideline và yêu cầu đề bài. Kết luận AI hợp lý vì đề yêu cầu booking phải bị hủy khi payment thất bại. Tôi bổ sung lời gọi updateStatus('Cancelled') trong sơ đồ.</t>
   </si>
 </sst>
 </file>
@@ -1696,73 +1724,73 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" ht="56" spans="1:5">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" ht="42" spans="1:5">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" ht="56" spans="1:5">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:5">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="3" t="s">
+    </row>
+    <row r="6" ht="56" spans="1:5">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="6" ht="56" spans="1:5">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1859,4 +1887,197 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8666666666667" customWidth="1"/>
+    <col min="3" max="3" width="30.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="50.5833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="49" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="98" spans="1:5">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" ht="70" spans="1:5">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" ht="98" spans="1:5">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" ht="70" spans="1:5">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" ht="70" spans="1:5">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Vo_Dinh_Tan.xlsx
+++ b/Vo_Dinh_Tan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12710" activeTab="4"/>
+    <workbookView windowWidth="24750" windowHeight="12710" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
     <sheet name="Week3" sheetId="4" r:id="rId4"/>
     <sheet name="Week4" sheetId="6" r:id="rId5"/>
+    <sheet name="Week5" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="90">
   <si>
     <t>STT</t>
   </si>
@@ -275,6 +276,36 @@
   </si>
   <si>
     <t>Phản hồi: AI đề xuất cập nhật trạng thái booking thành Cancelled thông qua BookingRepository. Kiểm chứng: Tôi tham khảo UML modeling guideline và yêu cầu đề bài. Kết luận AI hợp lý vì đề yêu cầu booking phải bị hủy khi payment thất bại. Tôi bổ sung lời gọi updateStatus('Cancelled') trong sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Đối với Order Lifecycle Management của nhà hàng, State Diagram nên có những trạng thái nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Created, Confirmed, Paid, Preparing, ReadyToServe, Served, Completed và Cancelled. Quyết định: Tôi đối chiếu với yêu cầu đề bài và xác nhận các trạng thái chính đều phù hợp. Tôi bổ sung PaymentFailed như một trạng thái kết thúc thay thế theo yêu cầu.</t>
+  </si>
+  <si>
+    <t>"Hãy mô tả luồng chuyển trạng thái của Order trong nhà hàng từ khi tạo đến khi hoàn thành."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả luồng Created → Confirmed → Paid → Preparing → ReadyToServe → Served → Completed. Kiểm chứng: Tôi so sánh với đề bài và thấy phù hợp. Tôi giữ nguyên luồng chính và thêm các sự kiện kích hoạt cho từng transition.</t>
+  </si>
+  <si>
+    <t>"Trong State Diagram này cần sử dụng những sự kiện (events) nào để chuyển trạng thái?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất confirmOrder, paySuccess, startCooking, finishCooking, serveOrder và closeOrder. Kiểm chứng: Đối chiếu yêu cầu đề, AI thiếu payFail. Tôi bổ sung payFail để xử lý trường hợp thanh toán thất bại.</t>
+  </si>
+  <si>
+    <t>"Làm thế nào để biểu diễn trường hợp thanh toán thất bại hoặc khách hủy đơn trong State Diagram?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất chuyển trực tiếp từ Created sang Cancelled. Kiểm chứng: Sau khi xem lại yêu cầu đề bài, tôi nhận thấy cần có ít nhất một nhánh thay thế cho PaymentFailed hoặc Cancelled. Tôi bổ sung transition từ Confirmed sang PaymentFailed thông qua sự kiện payFail để đáp ứng yêu cầu.</t>
+  </si>
+  <si>
+    <t>"Theo UML State Machine Diagram, trạng thái đầu và trạng thái cuối nên được biểu diễn như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích sử dụng Initial State (chấm đen) để bắt đầu và Final State (vòng tròn kép) để kết thúc vòng đời đối tượng. Kiểm chứng: Tôi đối chiếu với UML State Machine notation và yêu cầu đề bài, xác nhận AI giải thích đúng. Tôi áp dụng ký hiệu này trong sơ đồ và sử dụng hai nhánh kết thúc cho Completed và PaymentFailed/Cancelled.</t>
   </si>
 </sst>
 </file>
@@ -1917,72 +1948,72 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" ht="98" spans="1:5">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" ht="70" spans="1:5">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" ht="98" spans="1:5">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" ht="70" spans="1:5">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" ht="70" spans="1:5">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2080,4 +2111,197 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8666666666667" customWidth="1"/>
+    <col min="3" max="3" width="30.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="50.5833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="49" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="70" spans="1:5">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" ht="56" spans="1:5">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" ht="56" spans="1:5">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" ht="70" spans="1:5">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" ht="84" spans="1:5">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>